--- a/data/odds/Turf On Grade 2.0 2026 Betting Odds.xlsx
+++ b/data/odds/Turf On Grade 2.0 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="67">
   <si>
     <t>Record</t>
   </si>
@@ -30,196 +30,193 @@
     <t>Team</t>
   </si>
   <si>
+    <t>BHam Legion</t>
+  </si>
+  <si>
+    <t>Did I Set My Lineup?</t>
+  </si>
+  <si>
+    <t>Django Achane'd</t>
+  </si>
+  <si>
+    <t>OAC PADS</t>
+  </si>
+  <si>
+    <t>Team Date</t>
+  </si>
+  <si>
+    <t>RAJUN CAJUN</t>
+  </si>
+  <si>
+    <t>Trestleches</t>
+  </si>
+  <si>
+    <t>Masoud's Magnificent Team</t>
+  </si>
+  <si>
     <t>Control Machete</t>
   </si>
   <si>
-    <t>Trestleches</t>
-  </si>
-  <si>
-    <t>RAJUN CAJUN</t>
-  </si>
-  <si>
-    <t>Did I Set My Lineup?</t>
-  </si>
-  <si>
-    <t>BHam Legion</t>
-  </si>
-  <si>
-    <t>Masoud's Magnificent Team</t>
-  </si>
-  <si>
-    <t>OAC PADS</t>
-  </si>
-  <si>
-    <t>Team Date</t>
-  </si>
-  <si>
-    <t>Django Achane'd</t>
-  </si>
-  <si>
     <t>Jim-a-sore-ass</t>
   </si>
   <si>
     <t>0-0</t>
   </si>
   <si>
-    <t>42.6%</t>
-  </si>
-  <si>
-    <t>42.3%</t>
-  </si>
-  <si>
-    <t>41.2%</t>
+    <t>43.6%</t>
+  </si>
+  <si>
+    <t>43.0%</t>
+  </si>
+  <si>
+    <t>40.7%</t>
+  </si>
+  <si>
+    <t>40.6%</t>
   </si>
   <si>
     <t>40.2%</t>
   </si>
   <si>
-    <t>39.6%</t>
-  </si>
-  <si>
-    <t>39.4%</t>
-  </si>
-  <si>
-    <t>39.1%</t>
-  </si>
-  <si>
-    <t>38.4%</t>
-  </si>
-  <si>
-    <t>37.6%</t>
-  </si>
-  <si>
-    <t>+135</t>
-  </si>
-  <si>
-    <t>+136</t>
-  </si>
-  <si>
-    <t>+143</t>
+    <t>39.8%</t>
+  </si>
+  <si>
+    <t>38.3%</t>
+  </si>
+  <si>
+    <t>38.2%</t>
+  </si>
+  <si>
+    <t>37.8%</t>
+  </si>
+  <si>
+    <t>+129</t>
+  </si>
+  <si>
+    <t>+133</t>
+  </si>
+  <si>
+    <t>+146</t>
   </si>
   <si>
     <t>+149</t>
   </si>
   <si>
-    <t>+153</t>
-  </si>
-  <si>
-    <t>+154</t>
-  </si>
-  <si>
-    <t>+156</t>
-  </si>
-  <si>
-    <t>+160</t>
-  </si>
-  <si>
-    <t>+166</t>
+    <t>+151</t>
+  </si>
+  <si>
+    <t>+161</t>
+  </si>
+  <si>
+    <t>+162</t>
+  </si>
+  <si>
+    <t>+165</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
+    <t>12.3%</t>
+  </si>
+  <si>
     <t>11.6%</t>
   </si>
   <si>
-    <t>11.3%</t>
-  </si>
-  <si>
     <t>10.6%</t>
   </si>
   <si>
-    <t>10.5%</t>
+    <t>10.1%</t>
+  </si>
+  <si>
+    <t>9.7%</t>
+  </si>
+  <si>
+    <t>9.4%</t>
+  </si>
+  <si>
+    <t>9.2%</t>
+  </si>
+  <si>
+    <t>9.1%</t>
+  </si>
+  <si>
+    <t>8.9%</t>
+  </si>
+  <si>
+    <t>+713</t>
+  </si>
+  <si>
+    <t>+762</t>
+  </si>
+  <si>
+    <t>+843</t>
+  </si>
+  <si>
+    <t>+890</t>
+  </si>
+  <si>
+    <t>+931</t>
+  </si>
+  <si>
+    <t>+964</t>
+  </si>
+  <si>
+    <t>+987</t>
+  </si>
+  <si>
+    <t>+999</t>
+  </si>
+  <si>
+    <t>+1024</t>
+  </si>
+  <si>
+    <t>11.2%</t>
+  </si>
+  <si>
+    <t>10.7%</t>
+  </si>
+  <si>
+    <t>10.4%</t>
+  </si>
+  <si>
+    <t>10.3%</t>
+  </si>
+  <si>
+    <t>10.2%</t>
   </si>
   <si>
     <t>9.9%</t>
   </si>
   <si>
-    <t>9.4%</t>
-  </si>
-  <si>
-    <t>9.2%</t>
-  </si>
-  <si>
-    <t>8.8%</t>
-  </si>
-  <si>
-    <t>8.2%</t>
-  </si>
-  <si>
-    <t>+762</t>
-  </si>
-  <si>
-    <t>+785</t>
-  </si>
-  <si>
-    <t>+843</t>
-  </si>
-  <si>
-    <t>+852</t>
+    <t>9.8%</t>
+  </si>
+  <si>
+    <t>8.7%</t>
+  </si>
+  <si>
+    <t>+793</t>
+  </si>
+  <si>
+    <t>+835</t>
+  </si>
+  <si>
+    <t>+862</t>
+  </si>
+  <si>
+    <t>+871</t>
+  </si>
+  <si>
+    <t>+880</t>
   </si>
   <si>
     <t>+910</t>
   </si>
   <si>
-    <t>+964</t>
-  </si>
-  <si>
-    <t>+987</t>
-  </si>
-  <si>
-    <t>+1036</t>
-  </si>
-  <si>
-    <t>+1120</t>
-  </si>
-  <si>
-    <t>11.4%</t>
-  </si>
-  <si>
-    <t>10.7%</t>
-  </si>
-  <si>
-    <t>10.0%</t>
-  </si>
-  <si>
-    <t>9.7%</t>
-  </si>
-  <si>
-    <t>9.6%</t>
-  </si>
-  <si>
-    <t>9.3%</t>
-  </si>
-  <si>
-    <t>8.7%</t>
-  </si>
-  <si>
-    <t>8.5%</t>
-  </si>
-  <si>
-    <t>+777</t>
-  </si>
-  <si>
-    <t>+835</t>
-  </si>
-  <si>
-    <t>+900</t>
-  </si>
-  <si>
-    <t>+931</t>
-  </si>
-  <si>
-    <t>+942</t>
-  </si>
-  <si>
-    <t>+975</t>
+    <t>+920</t>
   </si>
   <si>
     <t>+1049</t>
-  </si>
-  <si>
-    <t>+1076</t>
   </si>
 </sst>
 </file>
@@ -647,7 +644,7 @@
         <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -661,7 +658,7 @@
         <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -672,7 +669,7 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
         <v>28</v>
@@ -686,7 +683,7 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
         <v>29</v>
@@ -700,7 +697,7 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
         <v>30</v>
@@ -714,7 +711,7 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
         <v>31</v>
@@ -731,7 +728,7 @@
         <v>23</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -752,7 +749,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -760,30 +757,30 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -794,10 +791,10 @@
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -808,15 +805,15 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
@@ -830,7 +827,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
@@ -844,7 +841,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
@@ -858,7 +855,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
@@ -872,30 +869,30 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -916,7 +913,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -924,21 +921,21 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -952,7 +949,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
@@ -972,43 +969,43 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="D5" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
@@ -1036,7 +1033,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
@@ -1050,16 +1047,16 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/Turf On Grade 2.0 2026 Betting Odds.xlsx
+++ b/data/odds/Turf On Grade 2.0 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="74">
   <si>
     <t>Record</t>
   </si>
@@ -30,88 +30,97 @@
     <t>Team</t>
   </si>
   <si>
+    <t>Control Machete</t>
+  </si>
+  <si>
+    <t>Django Achane'd</t>
+  </si>
+  <si>
+    <t>Did I Set My Lineup?</t>
+  </si>
+  <si>
+    <t>Trestleches</t>
+  </si>
+  <si>
+    <t>RAJUN CAJUN</t>
+  </si>
+  <si>
+    <t>Masoud's Magnificent Team</t>
+  </si>
+  <si>
+    <t>Team Date</t>
+  </si>
+  <si>
+    <t>OAC PADS</t>
+  </si>
+  <si>
     <t>BHam Legion</t>
   </si>
   <si>
-    <t>Did I Set My Lineup?</t>
-  </si>
-  <si>
-    <t>Django Achane'd</t>
-  </si>
-  <si>
-    <t>OAC PADS</t>
-  </si>
-  <si>
-    <t>Team Date</t>
-  </si>
-  <si>
-    <t>RAJUN CAJUN</t>
-  </si>
-  <si>
-    <t>Trestleches</t>
-  </si>
-  <si>
-    <t>Masoud's Magnificent Team</t>
-  </si>
-  <si>
-    <t>Control Machete</t>
-  </si>
-  <si>
     <t>Jim-a-sore-ass</t>
   </si>
   <si>
     <t>0-0</t>
   </si>
   <si>
-    <t>43.6%</t>
-  </si>
-  <si>
-    <t>43.0%</t>
-  </si>
-  <si>
-    <t>40.7%</t>
-  </si>
-  <si>
-    <t>40.6%</t>
-  </si>
-  <si>
-    <t>40.2%</t>
+    <t>43.5%</t>
+  </si>
+  <si>
+    <t>41.9%</t>
+  </si>
+  <si>
+    <t>40.9%</t>
+  </si>
+  <si>
+    <t>40.4%</t>
   </si>
   <si>
     <t>39.8%</t>
   </si>
   <si>
-    <t>38.3%</t>
-  </si>
-  <si>
-    <t>38.2%</t>
-  </si>
-  <si>
-    <t>37.8%</t>
-  </si>
-  <si>
-    <t>+129</t>
-  </si>
-  <si>
-    <t>+133</t>
-  </si>
-  <si>
-    <t>+146</t>
-  </si>
-  <si>
-    <t>+149</t>
+    <t>39.7%</t>
+  </si>
+  <si>
+    <t>39.5%</t>
+  </si>
+  <si>
+    <t>38.6%</t>
+  </si>
+  <si>
+    <t>38.1%</t>
+  </si>
+  <si>
+    <t>37.6%</t>
+  </si>
+  <si>
+    <t>+130</t>
+  </si>
+  <si>
+    <t>+139</t>
+  </si>
+  <si>
+    <t>+144</t>
+  </si>
+  <si>
+    <t>+148</t>
   </si>
   <si>
     <t>+151</t>
   </si>
   <si>
-    <t>+161</t>
+    <t>+152</t>
+  </si>
+  <si>
+    <t>+153</t>
+  </si>
+  <si>
+    <t>+159</t>
   </si>
   <si>
     <t>+162</t>
   </si>
   <si>
-    <t>+165</t>
+    <t>+166</t>
   </si>
   <si>
     <t>Probability</t>
@@ -120,16 +129,79 @@
     <t>12.3%</t>
   </si>
   <si>
-    <t>11.6%</t>
+    <t>11.7%</t>
+  </si>
+  <si>
+    <t>10.9%</t>
+  </si>
+  <si>
+    <t>10.8%</t>
+  </si>
+  <si>
+    <t>10.4%</t>
+  </si>
+  <si>
+    <t>9.7%</t>
+  </si>
+  <si>
+    <t>9.0%</t>
+  </si>
+  <si>
+    <t>8.8%</t>
+  </si>
+  <si>
+    <t>8.6%</t>
+  </si>
+  <si>
+    <t>7.8%</t>
+  </si>
+  <si>
+    <t>+713</t>
+  </si>
+  <si>
+    <t>+755</t>
+  </si>
+  <si>
+    <t>+817</t>
+  </si>
+  <si>
+    <t>+826</t>
+  </si>
+  <si>
+    <t>+862</t>
+  </si>
+  <si>
+    <t>+931</t>
+  </si>
+  <si>
+    <t>+1011</t>
+  </si>
+  <si>
+    <t>+1036</t>
+  </si>
+  <si>
+    <t>+1063</t>
+  </si>
+  <si>
+    <t>+1182</t>
+  </si>
+  <si>
+    <t>11.0%</t>
+  </si>
+  <si>
+    <t>10.7%</t>
   </si>
   <si>
     <t>10.6%</t>
   </si>
   <si>
-    <t>10.1%</t>
-  </si>
-  <si>
-    <t>9.7%</t>
+    <t>10.3%</t>
+  </si>
+  <si>
+    <t>9.8%</t>
+  </si>
+  <si>
+    <t>9.6%</t>
   </si>
   <si>
     <t>9.4%</t>
@@ -138,25 +210,25 @@
     <t>9.2%</t>
   </si>
   <si>
-    <t>9.1%</t>
-  </si>
-  <si>
-    <t>8.9%</t>
-  </si>
-  <si>
-    <t>+713</t>
-  </si>
-  <si>
-    <t>+762</t>
+    <t>8.5%</t>
+  </si>
+  <si>
+    <t>+809</t>
+  </si>
+  <si>
+    <t>+835</t>
   </si>
   <si>
     <t>+843</t>
   </si>
   <si>
-    <t>+890</t>
-  </si>
-  <si>
-    <t>+931</t>
+    <t>+871</t>
+  </si>
+  <si>
+    <t>+920</t>
+  </si>
+  <si>
+    <t>+942</t>
   </si>
   <si>
     <t>+964</t>
@@ -165,58 +237,7 @@
     <t>+987</t>
   </si>
   <si>
-    <t>+999</t>
-  </si>
-  <si>
-    <t>+1024</t>
-  </si>
-  <si>
-    <t>11.2%</t>
-  </si>
-  <si>
-    <t>10.7%</t>
-  </si>
-  <si>
-    <t>10.4%</t>
-  </si>
-  <si>
-    <t>10.3%</t>
-  </si>
-  <si>
-    <t>10.2%</t>
-  </si>
-  <si>
-    <t>9.9%</t>
-  </si>
-  <si>
-    <t>9.8%</t>
-  </si>
-  <si>
-    <t>8.7%</t>
-  </si>
-  <si>
-    <t>+793</t>
-  </si>
-  <si>
-    <t>+835</t>
-  </si>
-  <si>
-    <t>+862</t>
-  </si>
-  <si>
-    <t>+871</t>
-  </si>
-  <si>
-    <t>+880</t>
-  </si>
-  <si>
-    <t>+910</t>
-  </si>
-  <si>
-    <t>+920</t>
-  </si>
-  <si>
-    <t>+1049</t>
+    <t>+1076</t>
   </si>
 </sst>
 </file>
@@ -602,7 +623,7 @@
         <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -616,7 +637,7 @@
         <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -630,7 +651,7 @@
         <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -644,7 +665,7 @@
         <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -658,7 +679,7 @@
         <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -672,7 +693,7 @@
         <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -686,7 +707,7 @@
         <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -700,7 +721,7 @@
         <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -714,7 +735,7 @@
         <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -725,10 +746,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -749,7 +770,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -757,114 +778,114 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -875,24 +896,24 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -913,7 +934,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -921,142 +942,142 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D4" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D5" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D6" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D8" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D9" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D10" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D11" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/Turf On Grade 2.0 2026 Betting Odds.xlsx
+++ b/data/odds/Turf On Grade 2.0 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="70">
   <si>
     <t>Record</t>
   </si>
@@ -30,73 +30,70 @@
     <t>Team</t>
   </si>
   <si>
+    <t>OAC PADS</t>
+  </si>
+  <si>
+    <t>Did I Set My Lineup?</t>
+  </si>
+  <si>
+    <t>Jim-a-sore-ass</t>
+  </si>
+  <si>
+    <t>Trestleches</t>
+  </si>
+  <si>
+    <t>Masoud's Magnificent Team</t>
+  </si>
+  <si>
+    <t>RAJUN CAJUN</t>
+  </si>
+  <si>
+    <t>BHam Legion</t>
+  </si>
+  <si>
     <t>Control Machete</t>
   </si>
   <si>
     <t>Django Achane'd</t>
   </si>
   <si>
-    <t>Did I Set My Lineup?</t>
-  </si>
-  <si>
-    <t>Trestleches</t>
-  </si>
-  <si>
-    <t>RAJUN CAJUN</t>
-  </si>
-  <si>
-    <t>Masoud's Magnificent Team</t>
-  </si>
-  <si>
     <t>Team Date</t>
   </si>
   <si>
-    <t>OAC PADS</t>
-  </si>
-  <si>
-    <t>BHam Legion</t>
-  </si>
-  <si>
-    <t>Jim-a-sore-ass</t>
-  </si>
-  <si>
     <t>0-0</t>
   </si>
   <si>
-    <t>43.5%</t>
-  </si>
-  <si>
-    <t>41.9%</t>
+    <t>44.1%</t>
   </si>
   <si>
     <t>40.9%</t>
   </si>
   <si>
-    <t>40.4%</t>
-  </si>
-  <si>
-    <t>39.8%</t>
-  </si>
-  <si>
-    <t>39.7%</t>
+    <t>40.3%</t>
+  </si>
+  <si>
+    <t>39.9%</t>
+  </si>
+  <si>
+    <t>39.6%</t>
   </si>
   <si>
     <t>39.5%</t>
   </si>
   <si>
-    <t>38.6%</t>
-  </si>
-  <si>
-    <t>38.1%</t>
-  </si>
-  <si>
-    <t>37.6%</t>
-  </si>
-  <si>
-    <t>+130</t>
-  </si>
-  <si>
-    <t>+139</t>
+    <t>39.1%</t>
+  </si>
+  <si>
+    <t>39.0%</t>
+  </si>
+  <si>
+    <t>38.9%</t>
+  </si>
+  <si>
+    <t>38.7%</t>
+  </si>
+  <si>
+    <t>+127</t>
   </si>
   <si>
     <t>+144</t>
@@ -108,133 +105,124 @@
     <t>+151</t>
   </si>
   <si>
-    <t>+152</t>
-  </si>
-  <si>
     <t>+153</t>
   </si>
   <si>
-    <t>+159</t>
-  </si>
-  <si>
-    <t>+162</t>
-  </si>
-  <si>
-    <t>+166</t>
+    <t>+156</t>
+  </si>
+  <si>
+    <t>+157</t>
+  </si>
+  <si>
+    <t>+158</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>12.3%</t>
-  </si>
-  <si>
-    <t>11.7%</t>
-  </si>
-  <si>
-    <t>10.9%</t>
-  </si>
-  <si>
-    <t>10.8%</t>
-  </si>
-  <si>
-    <t>10.4%</t>
+    <t>12.9%</t>
+  </si>
+  <si>
+    <t>11.6%</t>
+  </si>
+  <si>
+    <t>10.5%</t>
+  </si>
+  <si>
+    <t>9.9%</t>
   </si>
   <si>
     <t>9.7%</t>
   </si>
   <si>
+    <t>9.5%</t>
+  </si>
+  <si>
+    <t>9.4%</t>
+  </si>
+  <si>
+    <t>9.1%</t>
+  </si>
+  <si>
     <t>9.0%</t>
   </si>
   <si>
-    <t>8.8%</t>
-  </si>
-  <si>
-    <t>8.6%</t>
-  </si>
-  <si>
-    <t>7.8%</t>
-  </si>
-  <si>
-    <t>+713</t>
-  </si>
-  <si>
-    <t>+755</t>
-  </si>
-  <si>
-    <t>+817</t>
-  </si>
-  <si>
-    <t>+826</t>
-  </si>
-  <si>
-    <t>+862</t>
+    <t>8.4%</t>
+  </si>
+  <si>
+    <t>+675</t>
+  </si>
+  <si>
+    <t>+762</t>
+  </si>
+  <si>
+    <t>+852</t>
+  </si>
+  <si>
+    <t>+910</t>
   </si>
   <si>
     <t>+931</t>
   </si>
   <si>
+    <t>+953</t>
+  </si>
+  <si>
+    <t>+964</t>
+  </si>
+  <si>
+    <t>+999</t>
+  </si>
+  <si>
     <t>+1011</t>
   </si>
   <si>
-    <t>+1036</t>
-  </si>
-  <si>
-    <t>+1063</t>
-  </si>
-  <si>
-    <t>+1182</t>
+    <t>+1090</t>
+  </si>
+  <si>
+    <t>11.5%</t>
   </si>
   <si>
     <t>11.0%</t>
   </si>
   <si>
-    <t>10.7%</t>
-  </si>
-  <si>
     <t>10.6%</t>
   </si>
   <si>
     <t>10.3%</t>
   </si>
   <si>
-    <t>9.8%</t>
-  </si>
-  <si>
-    <t>9.6%</t>
-  </si>
-  <si>
-    <t>9.4%</t>
+    <t>10.1%</t>
   </si>
   <si>
     <t>9.2%</t>
   </si>
   <si>
+    <t>8.7%</t>
+  </si>
+  <si>
     <t>8.5%</t>
   </si>
   <si>
+    <t>+770</t>
+  </si>
+  <si>
     <t>+809</t>
   </si>
   <si>
-    <t>+835</t>
-  </si>
-  <si>
     <t>+843</t>
   </si>
   <si>
     <t>+871</t>
   </si>
   <si>
-    <t>+920</t>
-  </si>
-  <si>
-    <t>+942</t>
-  </si>
-  <si>
-    <t>+964</t>
+    <t>+890</t>
   </si>
   <si>
     <t>+987</t>
+  </si>
+  <si>
+    <t>+1049</t>
   </si>
   <si>
     <t>+1076</t>
@@ -693,7 +681,7 @@
         <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -707,7 +695,7 @@
         <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -721,7 +709,7 @@
         <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -735,7 +723,7 @@
         <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -749,7 +737,7 @@
         <v>24</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -770,7 +758,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -778,142 +766,142 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -934,7 +922,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -942,142 +930,142 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="D3" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D6" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D8" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D10" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D11" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/Turf On Grade 2.0 2026 Betting Odds.xlsx
+++ b/data/odds/Turf On Grade 2.0 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="60">
   <si>
     <t>Record</t>
   </si>
@@ -33,199 +33,169 @@
     <t>OAC PADS</t>
   </si>
   <si>
+    <t>Team Date</t>
+  </si>
+  <si>
+    <t>BHam Legion</t>
+  </si>
+  <si>
+    <t>Trestleches</t>
+  </si>
+  <si>
+    <t>Django Achane'd</t>
+  </si>
+  <si>
+    <t>Masoud's Magnificent Team</t>
+  </si>
+  <si>
     <t>Did I Set My Lineup?</t>
   </si>
   <si>
+    <t>Control Machete</t>
+  </si>
+  <si>
     <t>Jim-a-sore-ass</t>
   </si>
   <si>
-    <t>Trestleches</t>
-  </si>
-  <si>
-    <t>Masoud's Magnificent Team</t>
-  </si>
-  <si>
     <t>RAJUN CAJUN</t>
   </si>
   <si>
-    <t>BHam Legion</t>
-  </si>
-  <si>
-    <t>Control Machete</t>
-  </si>
-  <si>
-    <t>Django Achane'd</t>
-  </si>
-  <si>
-    <t>Team Date</t>
-  </si>
-  <si>
     <t>0-0</t>
   </si>
   <si>
-    <t>44.1%</t>
-  </si>
-  <si>
-    <t>40.9%</t>
-  </si>
-  <si>
-    <t>40.3%</t>
-  </si>
-  <si>
-    <t>39.9%</t>
-  </si>
-  <si>
-    <t>39.6%</t>
+    <t>42.1%</t>
+  </si>
+  <si>
+    <t>42.0%</t>
+  </si>
+  <si>
+    <t>40.4%</t>
+  </si>
+  <si>
+    <t>40.0%</t>
   </si>
   <si>
     <t>39.5%</t>
   </si>
   <si>
+    <t>39.3%</t>
+  </si>
+  <si>
     <t>39.1%</t>
   </si>
   <si>
     <t>39.0%</t>
   </si>
   <si>
-    <t>38.9%</t>
-  </si>
-  <si>
-    <t>38.7%</t>
-  </si>
-  <si>
-    <t>+127</t>
-  </si>
-  <si>
-    <t>+144</t>
+    <t>+138</t>
   </si>
   <si>
     <t>+148</t>
   </si>
   <si>
-    <t>+151</t>
+    <t>+150</t>
   </si>
   <si>
     <t>+153</t>
   </si>
   <si>
+    <t>+154</t>
+  </si>
+  <si>
     <t>+156</t>
   </si>
   <si>
-    <t>+157</t>
-  </si>
-  <si>
-    <t>+158</t>
-  </si>
-  <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>12.9%</t>
-  </si>
-  <si>
-    <t>11.6%</t>
+    <t>11.0%</t>
+  </si>
+  <si>
+    <t>10.9%</t>
+  </si>
+  <si>
+    <t>10.7%</t>
+  </si>
+  <si>
+    <t>10.2%</t>
+  </si>
+  <si>
+    <t>9.7%</t>
+  </si>
+  <si>
+    <t>9.6%</t>
+  </si>
+  <si>
+    <t>8.9%</t>
+  </si>
+  <si>
+    <t>8.3%</t>
+  </si>
+  <si>
+    <t>+809</t>
+  </si>
+  <si>
+    <t>+817</t>
+  </si>
+  <si>
+    <t>+835</t>
+  </si>
+  <si>
+    <t>+880</t>
+  </si>
+  <si>
+    <t>+931</t>
+  </si>
+  <si>
+    <t>+942</t>
+  </si>
+  <si>
+    <t>+1024</t>
+  </si>
+  <si>
+    <t>+1105</t>
   </si>
   <si>
     <t>10.5%</t>
   </si>
   <si>
+    <t>10.4%</t>
+  </si>
+  <si>
+    <t>10.1%</t>
+  </si>
+  <si>
+    <t>10.0%</t>
+  </si>
+  <si>
     <t>9.9%</t>
   </si>
   <si>
-    <t>9.7%</t>
-  </si>
-  <si>
-    <t>9.5%</t>
-  </si>
-  <si>
-    <t>9.4%</t>
-  </si>
-  <si>
-    <t>9.1%</t>
-  </si>
-  <si>
-    <t>9.0%</t>
-  </si>
-  <si>
-    <t>8.4%</t>
-  </si>
-  <si>
-    <t>+675</t>
-  </si>
-  <si>
-    <t>+762</t>
+    <t>9.8%</t>
+  </si>
+  <si>
+    <t>8.7%</t>
   </si>
   <si>
     <t>+852</t>
   </si>
   <si>
+    <t>+862</t>
+  </si>
+  <si>
+    <t>+890</t>
+  </si>
+  <si>
+    <t>+900</t>
+  </si>
+  <si>
     <t>+910</t>
   </si>
   <si>
-    <t>+931</t>
-  </si>
-  <si>
-    <t>+953</t>
-  </si>
-  <si>
-    <t>+964</t>
-  </si>
-  <si>
-    <t>+999</t>
-  </si>
-  <si>
-    <t>+1011</t>
-  </si>
-  <si>
-    <t>+1090</t>
-  </si>
-  <si>
-    <t>11.5%</t>
-  </si>
-  <si>
-    <t>11.0%</t>
-  </si>
-  <si>
-    <t>10.6%</t>
-  </si>
-  <si>
-    <t>10.3%</t>
-  </si>
-  <si>
-    <t>10.1%</t>
-  </si>
-  <si>
-    <t>9.2%</t>
-  </si>
-  <si>
-    <t>8.7%</t>
-  </si>
-  <si>
-    <t>8.5%</t>
-  </si>
-  <si>
-    <t>+770</t>
-  </si>
-  <si>
-    <t>+809</t>
-  </si>
-  <si>
-    <t>+843</t>
-  </si>
-  <si>
-    <t>+871</t>
-  </si>
-  <si>
-    <t>+890</t>
-  </si>
-  <si>
-    <t>+987</t>
+    <t>+920</t>
   </si>
   <si>
     <t>+1049</t>
-  </si>
-  <si>
-    <t>+1076</t>
   </si>
 </sst>
 </file>
@@ -611,7 +581,7 @@
         <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -625,7 +595,7 @@
         <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -639,7 +609,7 @@
         <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -653,7 +623,7 @@
         <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -667,7 +637,7 @@
         <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -678,10 +648,10 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -692,10 +662,10 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -706,10 +676,10 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -720,10 +690,10 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -734,10 +704,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -758,7 +728,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -766,142 +736,142 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D11" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -922,7 +892,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -936,10 +906,10 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -950,52 +920,52 @@
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="D4" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D6" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1006,66 +976,66 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="D7" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D8" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="D9" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/Turf On Grade 2.0 2026 Betting Odds.xlsx
+++ b/data/odds/Turf On Grade 2.0 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="56">
   <si>
     <t>Record</t>
   </si>
@@ -30,70 +30,79 @@
     <t>Team</t>
   </si>
   <si>
+    <t>Team Date</t>
+  </si>
+  <si>
+    <t>RAJUN CAJUN</t>
+  </si>
+  <si>
+    <t>Control Machete</t>
+  </si>
+  <si>
+    <t>BHam Legion</t>
+  </si>
+  <si>
+    <t>Jim-a-sore-ass</t>
+  </si>
+  <si>
+    <t>Django Achane'd</t>
+  </si>
+  <si>
+    <t>Did I Set My Lineup?</t>
+  </si>
+  <si>
     <t>OAC PADS</t>
   </si>
   <si>
-    <t>Team Date</t>
-  </si>
-  <si>
-    <t>BHam Legion</t>
+    <t>Masoud's Magnificent Team</t>
   </si>
   <si>
     <t>Trestleches</t>
   </si>
   <si>
-    <t>Django Achane'd</t>
-  </si>
-  <si>
-    <t>Masoud's Magnificent Team</t>
-  </si>
-  <si>
-    <t>Did I Set My Lineup?</t>
-  </si>
-  <si>
-    <t>Control Machete</t>
-  </si>
-  <si>
-    <t>Jim-a-sore-ass</t>
-  </si>
-  <si>
-    <t>RAJUN CAJUN</t>
-  </si>
-  <si>
     <t>0-0</t>
   </si>
   <si>
-    <t>42.1%</t>
-  </si>
-  <si>
-    <t>42.0%</t>
-  </si>
-  <si>
-    <t>40.4%</t>
-  </si>
-  <si>
-    <t>40.0%</t>
-  </si>
-  <si>
-    <t>39.5%</t>
+    <t>43.0%</t>
+  </si>
+  <si>
+    <t>41.8%</t>
+  </si>
+  <si>
+    <t>40.6%</t>
+  </si>
+  <si>
+    <t>39.9%</t>
+  </si>
+  <si>
+    <t>39.7%</t>
+  </si>
+  <si>
+    <t>39.6%</t>
   </si>
   <si>
     <t>39.3%</t>
   </si>
   <si>
-    <t>39.1%</t>
-  </si>
-  <si>
-    <t>39.0%</t>
-  </si>
-  <si>
-    <t>+138</t>
-  </si>
-  <si>
-    <t>+148</t>
-  </si>
-  <si>
-    <t>+150</t>
+    <t>38.7%</t>
+  </si>
+  <si>
+    <t>37.8%</t>
+  </si>
+  <si>
+    <t>+133</t>
+  </si>
+  <si>
+    <t>+139</t>
+  </si>
+  <si>
+    <t>+146</t>
+  </si>
+  <si>
+    <t>+151</t>
+  </si>
+  <si>
+    <t>+152</t>
   </si>
   <si>
     <t>+153</t>
@@ -102,28 +111,61 @@
     <t>+154</t>
   </si>
   <si>
-    <t>+156</t>
+    <t>+158</t>
+  </si>
+  <si>
+    <t>+165</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>11.0%</t>
-  </si>
-  <si>
     <t>10.9%</t>
   </si>
   <si>
-    <t>10.7%</t>
-  </si>
-  <si>
-    <t>10.2%</t>
-  </si>
-  <si>
-    <t>9.7%</t>
-  </si>
-  <si>
-    <t>9.6%</t>
+    <t>10.8%</t>
+  </si>
+  <si>
+    <t>10.6%</t>
+  </si>
+  <si>
+    <t>10.5%</t>
+  </si>
+  <si>
+    <t>9.9%</t>
+  </si>
+  <si>
+    <t>9.8%</t>
+  </si>
+  <si>
+    <t>9.0%</t>
+  </si>
+  <si>
+    <t>+817</t>
+  </si>
+  <si>
+    <t>+826</t>
+  </si>
+  <si>
+    <t>+843</t>
+  </si>
+  <si>
+    <t>+852</t>
+  </si>
+  <si>
+    <t>+910</t>
+  </si>
+  <si>
+    <t>+920</t>
+  </si>
+  <si>
+    <t>+1011</t>
+  </si>
+  <si>
+    <t>12.3%</t>
+  </si>
+  <si>
+    <t>10.4%</t>
   </si>
   <si>
     <t>8.9%</t>
@@ -132,70 +174,16 @@
     <t>8.3%</t>
   </si>
   <si>
-    <t>+809</t>
-  </si>
-  <si>
-    <t>+817</t>
-  </si>
-  <si>
-    <t>+835</t>
-  </si>
-  <si>
-    <t>+880</t>
-  </si>
-  <si>
-    <t>+931</t>
-  </si>
-  <si>
-    <t>+942</t>
+    <t>+713</t>
+  </si>
+  <si>
+    <t>+862</t>
   </si>
   <si>
     <t>+1024</t>
   </si>
   <si>
     <t>+1105</t>
-  </si>
-  <si>
-    <t>10.5%</t>
-  </si>
-  <si>
-    <t>10.4%</t>
-  </si>
-  <si>
-    <t>10.1%</t>
-  </si>
-  <si>
-    <t>10.0%</t>
-  </si>
-  <si>
-    <t>9.9%</t>
-  </si>
-  <si>
-    <t>9.8%</t>
-  </si>
-  <si>
-    <t>8.7%</t>
-  </si>
-  <si>
-    <t>+852</t>
-  </si>
-  <si>
-    <t>+862</t>
-  </si>
-  <si>
-    <t>+890</t>
-  </si>
-  <si>
-    <t>+900</t>
-  </si>
-  <si>
-    <t>+910</t>
-  </si>
-  <si>
-    <t>+920</t>
-  </si>
-  <si>
-    <t>+1049</t>
   </si>
 </sst>
 </file>
@@ -581,7 +569,7 @@
         <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -595,7 +583,7 @@
         <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -609,7 +597,7 @@
         <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -623,7 +611,7 @@
         <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -637,7 +625,7 @@
         <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -648,10 +636,10 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -665,7 +653,7 @@
         <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -679,7 +667,7 @@
         <v>21</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -690,10 +678,10 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D10" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -704,10 +692,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -728,7 +716,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -742,122 +730,122 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -868,10 +856,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -892,7 +880,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -900,142 +888,142 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D10" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D11" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/Turf On Grade 2.0 2026 Betting Odds.xlsx
+++ b/data/odds/Turf On Grade 2.0 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="61">
   <si>
     <t>Record</t>
   </si>
@@ -30,160 +30,175 @@
     <t>Team</t>
   </si>
   <si>
+    <t>Django Achane'd</t>
+  </si>
+  <si>
+    <t>Trestleches</t>
+  </si>
+  <si>
+    <t>Control Machete</t>
+  </si>
+  <si>
     <t>Team Date</t>
   </si>
   <si>
+    <t>Jim-a-sore-ass</t>
+  </si>
+  <si>
+    <t>Did I Set My Lineup?</t>
+  </si>
+  <si>
+    <t>OAC PADS</t>
+  </si>
+  <si>
+    <t>Masoud's Magnificent Team</t>
+  </si>
+  <si>
     <t>RAJUN CAJUN</t>
   </si>
   <si>
-    <t>Control Machete</t>
-  </si>
-  <si>
     <t>BHam Legion</t>
   </si>
   <si>
-    <t>Jim-a-sore-ass</t>
-  </si>
-  <si>
-    <t>Django Achane'd</t>
-  </si>
-  <si>
-    <t>Did I Set My Lineup?</t>
-  </si>
-  <si>
-    <t>OAC PADS</t>
-  </si>
-  <si>
-    <t>Masoud's Magnificent Team</t>
-  </si>
-  <si>
-    <t>Trestleches</t>
-  </si>
-  <si>
     <t>0-0</t>
   </si>
   <si>
-    <t>43.0%</t>
-  </si>
-  <si>
-    <t>41.8%</t>
-  </si>
-  <si>
-    <t>40.6%</t>
-  </si>
-  <si>
-    <t>39.9%</t>
-  </si>
-  <si>
-    <t>39.7%</t>
-  </si>
-  <si>
-    <t>39.6%</t>
-  </si>
-  <si>
-    <t>39.3%</t>
+    <t>42.7%</t>
+  </si>
+  <si>
+    <t>42.3%</t>
+  </si>
+  <si>
+    <t>41.2%</t>
+  </si>
+  <si>
+    <t>40.0%</t>
+  </si>
+  <si>
+    <t>39.8%</t>
+  </si>
+  <si>
+    <t>39.4%</t>
+  </si>
+  <si>
+    <t>39.1%</t>
+  </si>
+  <si>
+    <t>38.8%</t>
   </si>
   <si>
     <t>38.7%</t>
   </si>
   <si>
-    <t>37.8%</t>
-  </si>
-  <si>
-    <t>+133</t>
-  </si>
-  <si>
-    <t>+139</t>
-  </si>
-  <si>
-    <t>+146</t>
+    <t>38.0%</t>
+  </si>
+  <si>
+    <t>+134</t>
+  </si>
+  <si>
+    <t>+136</t>
+  </si>
+  <si>
+    <t>+143</t>
+  </si>
+  <si>
+    <t>+150</t>
   </si>
   <si>
     <t>+151</t>
   </si>
   <si>
-    <t>+152</t>
-  </si>
-  <si>
-    <t>+153</t>
-  </si>
-  <si>
     <t>+154</t>
   </si>
   <si>
+    <t>+156</t>
+  </si>
+  <si>
     <t>+158</t>
   </si>
   <si>
-    <t>+165</t>
+    <t>+163</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
+    <t>11.5%</t>
+  </si>
+  <si>
+    <t>10.6%</t>
+  </si>
+  <si>
+    <t>10.5%</t>
+  </si>
+  <si>
+    <t>10.3%</t>
+  </si>
+  <si>
+    <t>10.1%</t>
+  </si>
+  <si>
+    <t>9.9%</t>
+  </si>
+  <si>
+    <t>9.5%</t>
+  </si>
+  <si>
+    <t>8.6%</t>
+  </si>
+  <si>
+    <t>8.4%</t>
+  </si>
+  <si>
+    <t>+770</t>
+  </si>
+  <si>
+    <t>+843</t>
+  </si>
+  <si>
+    <t>+852</t>
+  </si>
+  <si>
+    <t>+871</t>
+  </si>
+  <si>
+    <t>+890</t>
+  </si>
+  <si>
+    <t>+910</t>
+  </si>
+  <si>
+    <t>+953</t>
+  </si>
+  <si>
+    <t>+1063</t>
+  </si>
+  <si>
+    <t>+1090</t>
+  </si>
+  <si>
+    <t>11.1%</t>
+  </si>
+  <si>
     <t>10.9%</t>
   </si>
   <si>
-    <t>10.8%</t>
-  </si>
-  <si>
-    <t>10.6%</t>
-  </si>
-  <si>
-    <t>10.5%</t>
-  </si>
-  <si>
-    <t>9.9%</t>
-  </si>
-  <si>
-    <t>9.8%</t>
-  </si>
-  <si>
-    <t>9.0%</t>
+    <t>10.0%</t>
+  </si>
+  <si>
+    <t>8.8%</t>
+  </si>
+  <si>
+    <t>+801</t>
   </si>
   <si>
     <t>+817</t>
   </si>
   <si>
-    <t>+826</t>
-  </si>
-  <si>
-    <t>+843</t>
-  </si>
-  <si>
-    <t>+852</t>
-  </si>
-  <si>
-    <t>+910</t>
-  </si>
-  <si>
-    <t>+920</t>
-  </si>
-  <si>
-    <t>+1011</t>
-  </si>
-  <si>
-    <t>12.3%</t>
-  </si>
-  <si>
-    <t>10.4%</t>
-  </si>
-  <si>
-    <t>8.9%</t>
-  </si>
-  <si>
-    <t>8.3%</t>
-  </si>
-  <si>
-    <t>+713</t>
-  </si>
-  <si>
-    <t>+862</t>
-  </si>
-  <si>
-    <t>+1024</t>
-  </si>
-  <si>
-    <t>+1105</t>
+    <t>+900</t>
+  </si>
+  <si>
+    <t>+1036</t>
   </si>
 </sst>
 </file>
@@ -569,7 +584,7 @@
         <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -583,7 +598,7 @@
         <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -597,7 +612,7 @@
         <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -611,7 +626,7 @@
         <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -625,7 +640,7 @@
         <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -639,7 +654,7 @@
         <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -650,10 +665,10 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -664,10 +679,10 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -678,10 +693,10 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -692,10 +707,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -716,7 +731,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -724,30 +739,30 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -761,12 +776,12 @@
         <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -775,91 +790,91 @@
         <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -880,7 +895,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -888,86 +903,86 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="D3" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -978,52 +993,52 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
       </c>
       <c r="C10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" t="s">
         <v>50</v>
-      </c>
-      <c r="D10" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
